--- a/JsonConverter/ExcelFiles/EquipmentLevelData.xlsx
+++ b/JsonConverter/ExcelFiles/EquipmentLevelData.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+  <si>
+    <t>고유Id</t>
+  </si>
   <si>
     <t>레벨</t>
   </si>
@@ -25,10 +28,16 @@
     <t>레벨업 비용</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>float</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
   <si>
     <t>Level</t>
@@ -179,11 +188,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -192,7 +204,10 @@
     <xf borderId="3" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -200,6 +215,9 @@
     </xf>
     <xf borderId="6" fillId="3" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
@@ -436,10 +454,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="16.0"/>
-    <col customWidth="1" min="3" max="4" width="14.0"/>
-    <col customWidth="1" min="5" max="26" width="8.63"/>
+    <col customWidth="1" min="1" max="2" width="10.0"/>
+    <col customWidth="1" min="3" max="3" width="16.0"/>
+    <col customWidth="1" min="4" max="5" width="14.0"/>
+    <col customWidth="1" min="6" max="27" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -449,178 +467,217 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="7">
+      <c r="A4" s="9">
         <v>1.0</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="10">
         <v>1.0</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="11">
         <v>1.0</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="12">
         <v>0.0</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="7">
+      <c r="A5" s="9">
         <v>2.0</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="C5" s="11">
         <v>1.1</v>
       </c>
-      <c r="C5" s="8">
+      <c r="D5" s="11">
         <v>1.08</v>
       </c>
-      <c r="D5" s="9">
+      <c r="E5" s="12">
         <v>8.0</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>3.0</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="C6" s="11">
         <v>1.21</v>
       </c>
-      <c r="C6" s="8">
+      <c r="D6" s="11">
         <v>1.1664</v>
       </c>
-      <c r="D6" s="9">
+      <c r="E6" s="12">
         <v>12.0</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>4.0</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="10">
+        <v>4.0</v>
+      </c>
+      <c r="C7" s="11">
         <v>1.331</v>
       </c>
-      <c r="C7" s="8">
+      <c r="D7" s="11">
         <v>1.2597</v>
       </c>
-      <c r="D7" s="9">
+      <c r="E7" s="12">
         <v>16.0</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>5.0</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="10">
+        <v>5.0</v>
+      </c>
+      <c r="C8" s="11">
         <v>1.4641</v>
       </c>
-      <c r="C8" s="8">
+      <c r="D8" s="11">
         <v>1.3605</v>
       </c>
-      <c r="D8" s="9">
+      <c r="E8" s="12">
         <v>24.0</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="7">
+      <c r="A9" s="9">
         <v>6.0</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="10">
+        <v>6.0</v>
+      </c>
+      <c r="C9" s="11">
         <v>1.6105</v>
       </c>
-      <c r="C9" s="8">
+      <c r="D9" s="11">
         <v>1.4693</v>
       </c>
-      <c r="D9" s="9">
+      <c r="E9" s="12">
         <v>32.0</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="7">
+      <c r="A10" s="9">
         <v>7.0</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="10">
+        <v>7.0</v>
+      </c>
+      <c r="C10" s="11">
         <v>1.7716</v>
       </c>
-      <c r="C10" s="8">
+      <c r="D10" s="11">
         <v>1.5869</v>
       </c>
-      <c r="D10" s="9">
+      <c r="E10" s="12">
         <v>44.0</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="7">
+      <c r="A11" s="9">
         <v>8.0</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="10">
+        <v>8.0</v>
+      </c>
+      <c r="C11" s="11">
         <v>1.9487</v>
       </c>
-      <c r="C11" s="8">
+      <c r="D11" s="11">
         <v>1.7138</v>
       </c>
-      <c r="D11" s="9">
+      <c r="E11" s="12">
         <v>60.0</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="7">
+      <c r="A12" s="9">
         <v>9.0</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="10">
+        <v>9.0</v>
+      </c>
+      <c r="C12" s="11">
         <v>2.1436</v>
       </c>
-      <c r="C12" s="8">
+      <c r="D12" s="11">
         <v>1.8509</v>
       </c>
-      <c r="D12" s="9">
+      <c r="E12" s="12">
         <v>80.0</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="10">
+      <c r="A13" s="9">
         <v>10.0</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="C13" s="14">
         <v>2.3579</v>
       </c>
-      <c r="C13" s="11">
+      <c r="D13" s="14">
         <v>1.999</v>
       </c>
-      <c r="D13" s="12">
+      <c r="E13" s="15">
         <v>110.0</v>
       </c>
     </row>
